--- a/Team-Data/2014-15/4-15-2014-15.xlsx
+++ b/Team-Data/2014-15/4-15-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" t="n">
         <v>60</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>0.732</v>
+        <v>0.741</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
@@ -679,10 +746,10 @@
         <v>38.1</v>
       </c>
       <c r="J2" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.466</v>
+        <v>0.467</v>
       </c>
       <c r="L2" t="n">
         <v>10</v>
@@ -691,13 +758,13 @@
         <v>26.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.38</v>
+        <v>0.382</v>
       </c>
       <c r="O2" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P2" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q2" t="n">
         <v>0.778</v>
@@ -709,10 +776,10 @@
         <v>31.8</v>
       </c>
       <c r="T2" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="U2" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="V2" t="n">
         <v>14.2</v>
@@ -730,16 +797,16 @@
         <v>17.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.5</v>
+        <v>102.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -760,10 +827,10 @@
         <v>27</v>
       </c>
       <c r="AK2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL2" t="n">
         <v>4</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>5</v>
       </c>
       <c r="AM2" t="n">
         <v>7</v>
@@ -784,7 +851,7 @@
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>28</v>
@@ -799,7 +866,7 @@
         <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
         <v>18</v>
@@ -808,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F3" t="n">
         <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>0.488</v>
+        <v>0.481</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
@@ -861,10 +928,10 @@
         <v>38.9</v>
       </c>
       <c r="J3" t="n">
-        <v>87.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="K3" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L3" t="n">
         <v>8</v>
@@ -873,28 +940,28 @@
         <v>24.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.327</v>
+        <v>0.325</v>
       </c>
       <c r="O3" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P3" t="n">
         <v>20.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.754</v>
+        <v>0.756</v>
       </c>
       <c r="R3" t="n">
         <v>11.1</v>
       </c>
       <c r="S3" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T3" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="U3" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="V3" t="n">
         <v>13.8</v>
@@ -909,19 +976,19 @@
         <v>5.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.4</v>
+        <v>101.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
@@ -933,7 +1000,7 @@
         <v>16</v>
       </c>
       <c r="AH3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI3" t="n">
         <v>5</v>
@@ -945,7 +1012,7 @@
         <v>21</v>
       </c>
       <c r="AL3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM3" t="n">
         <v>13</v>
@@ -954,22 +1021,22 @@
         <v>27</v>
       </c>
       <c r="AO3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP3" t="n">
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
@@ -984,16 +1051,16 @@
         <v>30</v>
       </c>
       <c r="AY3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>22</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>21</v>
       </c>
       <c r="BA3" t="n">
         <v>26</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
         <v>18</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4" t="n">
         <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>0.463</v>
+        <v>0.457</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1061,13 +1128,13 @@
         <v>16.6</v>
       </c>
       <c r="P4" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.748</v>
+        <v>0.75</v>
       </c>
       <c r="R4" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S4" t="n">
         <v>32</v>
@@ -1100,22 +1167,22 @@
         <v>98</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.9</v>
+        <v>-3.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
         <v>18</v>
@@ -1124,7 +1191,7 @@
         <v>17</v>
       </c>
       <c r="AK4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>24</v>
@@ -1139,37 +1206,37 @@
         <v>18</v>
       </c>
       <c r="AP4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS4" t="n">
         <v>17</v>
       </c>
       <c r="AT4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU4" t="n">
         <v>21</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY4" t="n">
         <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
         <v>18</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -1207,46 +1274,46 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E5" t="n">
         <v>33</v>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>0.402</v>
+        <v>0.407</v>
       </c>
       <c r="H5" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="J5" t="n">
-        <v>84.5</v>
+        <v>84.7</v>
       </c>
       <c r="K5" t="n">
         <v>0.42</v>
       </c>
       <c r="L5" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.318</v>
+        <v>0.317</v>
       </c>
       <c r="O5" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P5" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.748</v>
+        <v>0.747</v>
       </c>
       <c r="R5" t="n">
         <v>10</v>
@@ -1255,7 +1322,7 @@
         <v>34.1</v>
       </c>
       <c r="T5" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="U5" t="n">
         <v>20.2</v>
@@ -1273,19 +1340,19 @@
         <v>5.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB5" t="n">
         <v>94.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1309,7 +1376,7 @@
         <v>29</v>
       </c>
       <c r="AL5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM5" t="n">
         <v>24</v>
@@ -1321,10 +1388,10 @@
         <v>13</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR5" t="n">
         <v>25</v>
@@ -1336,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1348,10 +1415,10 @@
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
         <v>9</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -1389,25 +1456,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>0.61</v>
+        <v>0.605</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
       </c>
       <c r="I6" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="K6" t="n">
         <v>0.442</v>
@@ -1416,10 +1483,10 @@
         <v>7.9</v>
       </c>
       <c r="M6" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O6" t="n">
         <v>19.7</v>
@@ -1428,61 +1495,61 @@
         <v>25.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.783</v>
+        <v>0.782</v>
       </c>
       <c r="R6" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S6" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="T6" t="n">
         <v>45.7</v>
       </c>
       <c r="U6" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V6" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W6" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X6" t="n">
         <v>5.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA6" t="n">
         <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="AC6" t="n">
         <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ6" t="n">
         <v>18</v>
@@ -1503,13 +1570,13 @@
         <v>3</v>
       </c>
       <c r="AP6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ6" t="n">
         <v>3</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
         <v>7</v>
@@ -1518,10 +1585,10 @@
         <v>3</v>
       </c>
       <c r="AU6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
         <v>28</v>
@@ -1530,10 +1597,10 @@
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA6" t="n">
         <v>6</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -1571,58 +1638,58 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F7" t="n">
         <v>29</v>
       </c>
       <c r="G7" t="n">
-        <v>0.646</v>
+        <v>0.642</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J7" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>0.458</v>
       </c>
       <c r="L7" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0.367</v>
+        <v>0.364</v>
       </c>
       <c r="O7" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P7" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="R7" t="n">
         <v>11.1</v>
       </c>
       <c r="S7" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T7" t="n">
         <v>43</v>
       </c>
       <c r="U7" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V7" t="n">
         <v>14.3</v>
@@ -1640,16 +1707,16 @@
         <v>18.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>103.1</v>
+        <v>103</v>
       </c>
       <c r="AC7" t="n">
         <v>4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
@@ -1667,7 +1734,7 @@
         <v>15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK7" t="n">
         <v>8</v>
@@ -1679,10 +1746,10 @@
         <v>2</v>
       </c>
       <c r="AN7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP7" t="n">
         <v>11</v>
@@ -1691,10 +1758,10 @@
         <v>17</v>
       </c>
       <c r="AR7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AT7" t="n">
         <v>18</v>
@@ -1724,7 +1791,7 @@
         <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -1756,13 +1823,13 @@
         <v>81</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>0.617</v>
+        <v>0.605</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1771,10 +1838,10 @@
         <v>39.7</v>
       </c>
       <c r="J8" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L8" t="n">
         <v>8.9</v>
@@ -1786,28 +1853,28 @@
         <v>0.351</v>
       </c>
       <c r="O8" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P8" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="Q8" t="n">
         <v>0.751</v>
       </c>
       <c r="R8" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="T8" t="n">
-        <v>42.4</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
         <v>22.6</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W8" t="n">
         <v>8.1</v>
@@ -1819,25 +1886,25 @@
         <v>3.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>105.3</v>
+        <v>105.1</v>
       </c>
       <c r="AC8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD8" t="n">
         <v>3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>25</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
         <v>9</v>
@@ -1849,7 +1916,7 @@
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
@@ -1864,10 +1931,10 @@
         <v>13</v>
       </c>
       <c r="AO8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ8" t="n">
         <v>18</v>
@@ -1876,22 +1943,22 @@
         <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -1935,61 +2002,61 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E9" t="n">
         <v>30</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>0.366</v>
+        <v>0.37</v>
       </c>
       <c r="H9" t="n">
         <v>48.5</v>
       </c>
       <c r="I9" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J9" t="n">
         <v>87.3</v>
       </c>
       <c r="K9" t="n">
-        <v>0.433</v>
+        <v>0.432</v>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M9" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="N9" t="n">
         <v>0.325</v>
       </c>
       <c r="O9" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P9" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.734</v>
+        <v>0.732</v>
       </c>
       <c r="R9" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S9" t="n">
         <v>32.4</v>
       </c>
       <c r="T9" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="U9" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V9" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W9" t="n">
         <v>7.8</v>
@@ -2001,19 +2068,19 @@
         <v>6.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AA9" t="n">
         <v>20.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>101.5</v>
+        <v>101.2</v>
       </c>
       <c r="AC9" t="n">
         <v>-3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2025,10 +2092,10 @@
         <v>24</v>
       </c>
       <c r="AH9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ9" t="n">
         <v>2</v>
@@ -2046,7 +2113,7 @@
         <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
         <v>8</v>
@@ -2058,22 +2125,22 @@
         <v>3</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
       </c>
       <c r="AU9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AV9" t="n">
         <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY9" t="n">
         <v>29</v>
@@ -2085,7 +2152,7 @@
         <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC9" t="n">
         <v>24</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E10" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F10" t="n">
         <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>0.39</v>
+        <v>0.383</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J10" t="n">
-        <v>85.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
       <c r="L10" t="n">
         <v>8.6</v>
@@ -2150,13 +2217,13 @@
         <v>0.344</v>
       </c>
       <c r="O10" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="P10" t="n">
         <v>22.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.703</v>
+        <v>0.702</v>
       </c>
       <c r="R10" t="n">
         <v>12.8</v>
@@ -2174,7 +2241,7 @@
         <v>13.4</v>
       </c>
       <c r="W10" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X10" t="n">
         <v>4.7</v>
@@ -2189,13 +2256,13 @@
         <v>19.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>98.5</v>
+        <v>98.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1</v>
+        <v>-1.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2213,7 +2280,7 @@
         <v>20</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK10" t="n">
         <v>27</v>
@@ -2225,25 +2292,25 @@
         <v>11</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO10" t="n">
         <v>26</v>
       </c>
       <c r="AP10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
       </c>
       <c r="AR10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS10" t="n">
         <v>16</v>
       </c>
       <c r="AT10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU10" t="n">
         <v>16</v>
@@ -2252,22 +2319,22 @@
         <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX10" t="n">
         <v>13</v>
       </c>
       <c r="AY10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ10" t="n">
         <v>7</v>
       </c>
       <c r="BA10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -2299,43 +2366,43 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F11" t="n">
         <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
       </c>
       <c r="I11" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="J11" t="n">
         <v>87</v>
       </c>
       <c r="K11" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="L11" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="M11" t="n">
         <v>27</v>
       </c>
       <c r="N11" t="n">
-        <v>0.398</v>
+        <v>0.397</v>
       </c>
       <c r="O11" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P11" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="Q11" t="n">
         <v>0.768</v>
@@ -2344,10 +2411,10 @@
         <v>10.4</v>
       </c>
       <c r="S11" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="T11" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="U11" t="n">
         <v>27.4</v>
@@ -2365,19 +2432,19 @@
         <v>3.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>110</v>
+        <v>109.7</v>
       </c>
       <c r="AC11" t="n">
         <v>10.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2410,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP11" t="n">
         <v>26</v>
@@ -2446,7 +2513,7 @@
         <v>13</v>
       </c>
       <c r="BA11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -2496,13 +2563,13 @@
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J12" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L12" t="n">
         <v>11.4</v>
@@ -2514,52 +2581,52 @@
         <v>0.347</v>
       </c>
       <c r="O12" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P12" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="Q12" t="n">
         <v>0.716</v>
       </c>
       <c r="R12" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S12" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="T12" t="n">
         <v>43.6</v>
       </c>
       <c r="U12" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="V12" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="W12" t="n">
         <v>9.5</v>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.9</v>
+        <v>103.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2592,19 +2659,19 @@
         <v>14</v>
       </c>
       <c r="AO12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
       </c>
       <c r="AR12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT12" t="n">
         <v>15</v>
@@ -2619,10 +2686,10 @@
         <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ12" t="n">
         <v>27</v>
@@ -2631,7 +2698,7 @@
         <v>7</v>
       </c>
       <c r="BB12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E13" t="n">
         <v>38</v>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>0.463</v>
+        <v>0.469</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2681,10 +2748,10 @@
         <v>36.6</v>
       </c>
       <c r="J13" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L13" t="n">
         <v>7.5</v>
@@ -2696,7 +2763,7 @@
         <v>0.352</v>
       </c>
       <c r="O13" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P13" t="n">
         <v>22.2</v>
@@ -2708,22 +2775,22 @@
         <v>10.4</v>
       </c>
       <c r="S13" t="n">
-        <v>34.4</v>
+        <v>34.6</v>
       </c>
       <c r="T13" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="U13" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V13" t="n">
         <v>14</v>
       </c>
       <c r="W13" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y13" t="n">
         <v>4.7</v>
@@ -2735,19 +2802,19 @@
         <v>21.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.3</v>
+        <v>97.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
         <v>18</v>
       </c>
       <c r="AF13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG13" t="n">
         <v>18</v>
@@ -2756,7 +2823,7 @@
         <v>13</v>
       </c>
       <c r="AI13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ13" t="n">
         <v>15</v>
@@ -2765,7 +2832,7 @@
         <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
@@ -2774,7 +2841,7 @@
         <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP13" t="n">
         <v>18</v>
@@ -2789,7 +2856,7 @@
         <v>3</v>
       </c>
       <c r="AT13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU13" t="n">
         <v>18</v>
@@ -2801,13 +2868,13 @@
         <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY13" t="n">
         <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA13" t="n">
         <v>4</v>
@@ -2816,7 +2883,7 @@
         <v>24</v>
       </c>
       <c r="BC13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -2935,13 +3002,13 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AI14" t="n">
         <v>3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK14" t="n">
         <v>2</v>
@@ -2980,7 +3047,7 @@
         <v>2</v>
       </c>
       <c r="AW14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX14" t="n">
         <v>9</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -3042,10 +3109,10 @@
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>85.7</v>
+        <v>85.5</v>
       </c>
       <c r="K15" t="n">
         <v>0.436</v>
@@ -3054,58 +3121,58 @@
         <v>6.5</v>
       </c>
       <c r="M15" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O15" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P15" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.739</v>
+        <v>0.74</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T15" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U15" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V15" t="n">
         <v>13.2</v>
       </c>
       <c r="W15" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z15" t="n">
         <v>21.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>98.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.7</v>
+        <v>-6.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,7 +3184,7 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI15" t="n">
         <v>19</v>
@@ -3150,10 +3217,10 @@
         <v>8</v>
       </c>
       <c r="AS15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
         <v>20</v>
@@ -3165,7 +3232,7 @@
         <v>22</v>
       </c>
       <c r="AX15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY15" t="n">
         <v>17</v>
@@ -3174,7 +3241,7 @@
         <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB15" t="n">
         <v>17</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -3209,25 +3276,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E16" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F16" t="n">
         <v>27</v>
       </c>
       <c r="G16" t="n">
-        <v>0.671</v>
+        <v>0.667</v>
       </c>
       <c r="H16" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I16" t="n">
         <v>37.8</v>
       </c>
       <c r="J16" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>0.458</v>
@@ -3236,10 +3303,10 @@
         <v>5.2</v>
       </c>
       <c r="M16" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.339</v>
+        <v>0.34</v>
       </c>
       <c r="O16" t="n">
         <v>17.6</v>
@@ -3257,10 +3324,10 @@
         <v>32.1</v>
       </c>
       <c r="T16" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U16" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V16" t="n">
         <v>13.3</v>
@@ -3272,43 +3339,43 @@
         <v>4.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z16" t="n">
         <v>19.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>98.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH16" t="n">
         <v>6</v>
       </c>
       <c r="AI16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ16" t="n">
         <v>23</v>
       </c>
       <c r="AK16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3317,19 +3384,19 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>10</v>
       </c>
       <c r="AP16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ16" t="n">
         <v>7</v>
       </c>
       <c r="AR16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS16" t="n">
         <v>15</v>
@@ -3338,13 +3405,13 @@
         <v>21</v>
       </c>
       <c r="AU16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV16" t="n">
         <v>7</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX16" t="n">
         <v>24</v>
@@ -3353,13 +3420,13 @@
         <v>20</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC16" t="n">
         <v>8</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -3391,40 +3458,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F17" t="n">
         <v>45</v>
       </c>
       <c r="G17" t="n">
-        <v>0.451</v>
+        <v>0.444</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
       </c>
       <c r="I17" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="J17" t="n">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="K17" t="n">
         <v>0.456</v>
       </c>
       <c r="L17" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M17" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.335</v>
+        <v>0.334</v>
       </c>
       <c r="O17" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P17" t="n">
         <v>23.7</v>
@@ -3451,7 +3518,7 @@
         <v>7.8</v>
       </c>
       <c r="X17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y17" t="n">
         <v>4.4</v>
@@ -3463,13 +3530,13 @@
         <v>20.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-2.6</v>
+        <v>-2.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
         <v>21</v>
@@ -3484,7 +3551,7 @@
         <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3526,10 +3593,10 @@
         <v>21</v>
       </c>
       <c r="AW17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX17" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AY17" t="n">
         <v>8</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E18" t="n">
         <v>41</v>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.506</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
@@ -3591,7 +3658,7 @@
         <v>37.6</v>
       </c>
       <c r="J18" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K18" t="n">
         <v>0.459</v>
@@ -3603,55 +3670,55 @@
         <v>18.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="O18" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P18" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="Q18" t="n">
         <v>0.757</v>
       </c>
       <c r="R18" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S18" t="n">
         <v>31.4</v>
       </c>
       <c r="T18" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U18" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="V18" t="n">
         <v>16.7</v>
       </c>
       <c r="W18" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="n">
         <v>4.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB18" t="n">
         <v>97.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
         <v>15</v>
@@ -3663,7 +3730,7 @@
         <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="n">
         <v>16</v>
@@ -3684,7 +3751,7 @@
         <v>7</v>
       </c>
       <c r="AO18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP18" t="n">
         <v>25</v>
@@ -3711,10 +3778,10 @@
         <v>1</v>
       </c>
       <c r="AX18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ18" t="n">
         <v>28</v>
@@ -3726,7 +3793,7 @@
         <v>22</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E19" t="n">
         <v>16</v>
       </c>
       <c r="F19" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G19" t="n">
-        <v>0.195</v>
+        <v>0.198</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
@@ -3779,7 +3846,7 @@
         <v>0.438</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M19" t="n">
         <v>14.9</v>
@@ -3788,19 +3855,19 @@
         <v>0.332</v>
       </c>
       <c r="O19" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P19" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R19" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S19" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T19" t="n">
         <v>40.9</v>
@@ -3821,19 +3888,19 @@
         <v>5.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
         <v>30</v>
@@ -3845,7 +3912,7 @@
         <v>30</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI19" t="n">
         <v>25</v>
@@ -3869,7 +3936,7 @@
         <v>2</v>
       </c>
       <c r="AP19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ19" t="n">
         <v>6</v>
@@ -3884,7 +3951,7 @@
         <v>27</v>
       </c>
       <c r="AU19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV19" t="n">
         <v>23</v>
@@ -3899,7 +3966,7 @@
         <v>26</v>
       </c>
       <c r="AZ19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA19" t="n">
         <v>5</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -3952,40 +4019,40 @@
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J20" t="n">
-        <v>82.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
         <v>7.2</v>
       </c>
       <c r="M20" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.372</v>
+        <v>0.369</v>
       </c>
       <c r="O20" t="n">
         <v>16.4</v>
       </c>
       <c r="P20" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.756</v>
+        <v>0.752</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T20" t="n">
-        <v>43.2</v>
+        <v>43.6</v>
       </c>
       <c r="U20" t="n">
         <v>22</v>
@@ -3997,7 +4064,7 @@
         <v>6.7</v>
       </c>
       <c r="X20" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
@@ -4006,25 +4073,25 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
         <v>23</v>
@@ -4033,10 +4100,10 @@
         <v>12</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL20" t="n">
         <v>19</v>
@@ -4054,13 +4121,13 @@
         <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT20" t="n">
         <v>16</v>
@@ -4072,7 +4139,7 @@
         <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX20" t="n">
         <v>1</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21" t="n">
         <v>17</v>
       </c>
       <c r="F21" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G21" t="n">
-        <v>0.207</v>
+        <v>0.21</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="J21" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>0.428</v>
@@ -4152,13 +4219,13 @@
         <v>0.347</v>
       </c>
       <c r="O21" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="P21" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.769</v>
+        <v>0.771</v>
       </c>
       <c r="R21" t="n">
         <v>10.6</v>
@@ -4173,7 +4240,7 @@
         <v>21.3</v>
       </c>
       <c r="V21" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W21" t="n">
         <v>7</v>
@@ -4188,16 +4255,16 @@
         <v>21.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AB21" t="n">
         <v>91.90000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
         <v>29</v>
@@ -4212,10 +4279,10 @@
         <v>13</v>
       </c>
       <c r="AI21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK21" t="n">
         <v>28</v>
@@ -4233,7 +4300,7 @@
         <v>29</v>
       </c>
       <c r="AP21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ21" t="n">
         <v>8</v>
@@ -4251,10 +4318,10 @@
         <v>19</v>
       </c>
       <c r="AV21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX21" t="n">
         <v>14</v>
@@ -4269,7 +4336,7 @@
         <v>25</v>
       </c>
       <c r="BB21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F22" t="n">
         <v>37</v>
       </c>
       <c r="G22" t="n">
-        <v>0.549</v>
+        <v>0.543</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="J22" t="n">
-        <v>86.8</v>
+        <v>86.7</v>
       </c>
       <c r="K22" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L22" t="n">
         <v>7.7</v>
@@ -4331,22 +4398,22 @@
         <v>22.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.339</v>
+        <v>0.338</v>
       </c>
       <c r="O22" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="P22" t="n">
         <v>24.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
       <c r="R22" t="n">
         <v>12.8</v>
       </c>
       <c r="S22" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="T22" t="n">
         <v>47.5</v>
@@ -4373,13 +4440,13 @@
         <v>20.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>104</v>
+        <v>103.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
@@ -4394,19 +4461,19 @@
         <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ22" t="n">
         <v>4</v>
       </c>
       <c r="AK22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL22" t="n">
         <v>16</v>
       </c>
       <c r="AM22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN22" t="n">
         <v>23</v>
@@ -4415,13 +4482,13 @@
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS22" t="n">
         <v>2</v>
@@ -4430,10 +4497,10 @@
         <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW22" t="n">
         <v>21</v>
@@ -4442,16 +4509,16 @@
         <v>6</v>
       </c>
       <c r="AY22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ22" t="n">
         <v>29</v>
       </c>
       <c r="BA22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -4498,40 +4565,40 @@
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J23" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L23" t="n">
         <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N23" t="n">
         <v>0.347</v>
       </c>
       <c r="O23" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="P23" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.729</v>
+        <v>0.732</v>
       </c>
       <c r="R23" t="n">
         <v>10</v>
       </c>
       <c r="S23" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="U23" t="n">
         <v>20.7</v>
@@ -4546,13 +4613,13 @@
         <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
         <v>20.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="AB23" t="n">
         <v>95.8</v>
@@ -4561,7 +4628,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4573,7 +4640,7 @@
         <v>26</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
         <v>17</v>
@@ -4597,22 +4664,22 @@
         <v>30</v>
       </c>
       <c r="AP23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ23" t="n">
         <v>25</v>
       </c>
       <c r="AR23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
         <v>25</v>
       </c>
       <c r="AU23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV23" t="n">
         <v>22</v>
@@ -4624,10 +4691,10 @@
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" t="n">
         <v>18</v>
       </c>
       <c r="F24" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G24" t="n">
-        <v>0.22</v>
+        <v>0.222</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
@@ -4686,25 +4753,25 @@
         <v>82.59999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.408</v>
+        <v>0.407</v>
       </c>
       <c r="L24" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="M24" t="n">
         <v>26.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0.32</v>
+        <v>0.322</v>
       </c>
       <c r="O24" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="P24" t="n">
         <v>23.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.676</v>
+        <v>0.674</v>
       </c>
       <c r="R24" t="n">
         <v>11.9</v>
@@ -4713,7 +4780,7 @@
         <v>30.9</v>
       </c>
       <c r="T24" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U24" t="n">
         <v>20.5</v>
@@ -4722,13 +4789,13 @@
         <v>17.7</v>
       </c>
       <c r="W24" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z24" t="n">
         <v>21.7</v>
@@ -4737,13 +4804,13 @@
         <v>20.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>92</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AC24" t="n">
         <v>-9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4776,7 +4843,7 @@
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP24" t="n">
         <v>9</v>
@@ -4794,7 +4861,7 @@
         <v>19</v>
       </c>
       <c r="AU24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4812,10 +4879,10 @@
         <v>26</v>
       </c>
       <c r="BA24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC24" t="n">
         <v>29</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4995,7 @@
         <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF25" t="n">
         <v>17</v>
@@ -4937,10 +5004,10 @@
         <v>17</v>
       </c>
       <c r="AH25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AI25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ25" t="n">
         <v>7</v>
@@ -4955,7 +5022,7 @@
         <v>10</v>
       </c>
       <c r="AN25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO25" t="n">
         <v>21</v>
@@ -4967,7 +5034,7 @@
         <v>11</v>
       </c>
       <c r="AR25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS25" t="n">
         <v>14</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E26" t="n">
         <v>51</v>
       </c>
       <c r="F26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" t="n">
-        <v>0.622</v>
+        <v>0.63</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5047,19 +5114,19 @@
         <v>38.7</v>
       </c>
       <c r="J26" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="M26" t="n">
         <v>27.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O26" t="n">
         <v>15.5</v>
@@ -5068,19 +5135,19 @@
         <v>19.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.801</v>
+        <v>0.8</v>
       </c>
       <c r="R26" t="n">
         <v>10.7</v>
       </c>
       <c r="S26" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="T26" t="n">
         <v>45.9</v>
       </c>
       <c r="U26" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V26" t="n">
         <v>13.6</v>
@@ -5101,13 +5168,13 @@
         <v>18.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>102.8</v>
+        <v>102.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
@@ -5122,13 +5189,13 @@
         <v>13</v>
       </c>
       <c r="AI26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ26" t="n">
         <v>5</v>
       </c>
       <c r="AK26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
         <v>6</v>
@@ -5140,7 +5207,7 @@
         <v>8</v>
       </c>
       <c r="AO26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP26" t="n">
         <v>28</v>
@@ -5167,7 +5234,7 @@
         <v>27</v>
       </c>
       <c r="AX26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5176,13 +5243,13 @@
         <v>2</v>
       </c>
       <c r="BA26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB26" t="n">
         <v>9</v>
       </c>
       <c r="BC26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F27" t="n">
         <v>53</v>
       </c>
       <c r="G27" t="n">
-        <v>0.354</v>
+        <v>0.346</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J27" t="n">
         <v>80.7</v>
       </c>
       <c r="K27" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L27" t="n">
         <v>5.6</v>
@@ -5241,28 +5308,28 @@
         <v>16.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O27" t="n">
         <v>22.3</v>
       </c>
       <c r="P27" t="n">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.762</v>
+        <v>0.766</v>
       </c>
       <c r="R27" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S27" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="T27" t="n">
         <v>44.2</v>
       </c>
       <c r="U27" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V27" t="n">
         <v>16.3</v>
@@ -5280,16 +5347,16 @@
         <v>20.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.3</v>
+        <v>101.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>-3.7</v>
+        <v>-4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5304,7 +5371,7 @@
         <v>13</v>
       </c>
       <c r="AI27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5331,7 +5398,7 @@
         <v>10</v>
       </c>
       <c r="AR27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS27" t="n">
         <v>9</v>
@@ -5340,13 +5407,13 @@
         <v>9</v>
       </c>
       <c r="AU27" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -5396,37 +5463,37 @@
         <v>81</v>
       </c>
       <c r="E28" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>0.667</v>
+        <v>0.679</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
       </c>
       <c r="I28" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K28" t="n">
         <v>0.467</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.364</v>
+        <v>0.367</v>
       </c>
       <c r="O28" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P28" t="n">
         <v>21.5</v>
@@ -5435,22 +5502,22 @@
         <v>0.78</v>
       </c>
       <c r="R28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T28" t="n">
         <v>43.7</v>
       </c>
       <c r="U28" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W28" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X28" t="n">
         <v>5.4</v>
@@ -5471,16 +5538,16 @@
         <v>6.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
@@ -5492,16 +5559,16 @@
         <v>11</v>
       </c>
       <c r="AK28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL28" t="n">
         <v>12</v>
       </c>
       <c r="AM28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
         <v>17</v>
@@ -5525,10 +5592,10 @@
         <v>5</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX28" t="n">
         <v>8</v>
@@ -5540,7 +5607,7 @@
         <v>8</v>
       </c>
       <c r="BA28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB28" t="n">
         <v>7</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E29" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F29" t="n">
         <v>33</v>
       </c>
       <c r="G29" t="n">
-        <v>0.598</v>
+        <v>0.593</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
@@ -5593,37 +5660,37 @@
         <v>37.9</v>
       </c>
       <c r="J29" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>0.455</v>
       </c>
       <c r="L29" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="N29" t="n">
         <v>0.352</v>
       </c>
       <c r="O29" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="P29" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="Q29" t="n">
         <v>0.787</v>
       </c>
       <c r="R29" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S29" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T29" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="U29" t="n">
         <v>20.7</v>
@@ -5638,22 +5705,22 @@
         <v>4.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z29" t="n">
         <v>20.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>104</v>
+        <v>104.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5671,7 +5738,7 @@
         <v>11</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK29" t="n">
         <v>12</v>
@@ -5689,7 +5756,7 @@
         <v>4</v>
       </c>
       <c r="AP29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="n">
         <v>2</v>
@@ -5722,7 +5789,7 @@
         <v>19</v>
       </c>
       <c r="BA29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB29" t="n">
         <v>4</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -5757,46 +5824,46 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E30" t="n">
         <v>38</v>
       </c>
       <c r="F30" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G30" t="n">
-        <v>0.463</v>
+        <v>0.469</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J30" t="n">
-        <v>79.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L30" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M30" t="n">
         <v>21.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.343</v>
+        <v>0.345</v>
       </c>
       <c r="O30" t="n">
         <v>17</v>
       </c>
       <c r="P30" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.721</v>
+        <v>0.723</v>
       </c>
       <c r="R30" t="n">
         <v>12</v>
@@ -5814,13 +5881,13 @@
         <v>15.3</v>
       </c>
       <c r="W30" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X30" t="n">
         <v>6</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z30" t="n">
         <v>19.3</v>
@@ -5829,19 +5896,19 @@
         <v>19.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>18</v>
       </c>
       <c r="AF30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG30" t="n">
         <v>18</v>
@@ -5856,16 +5923,16 @@
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM30" t="n">
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO30" t="n">
         <v>14</v>
@@ -5883,7 +5950,7 @@
         <v>19</v>
       </c>
       <c r="AT30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU30" t="n">
         <v>29</v>
@@ -5898,10 +5965,10 @@
         <v>3</v>
       </c>
       <c r="AY30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA30" t="n">
         <v>22</v>
@@ -5910,7 +5977,7 @@
         <v>26</v>
       </c>
       <c r="BC30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
@@ -5939,31 +6006,31 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E31" t="n">
         <v>46</v>
       </c>
       <c r="F31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J31" t="n">
-        <v>82.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L31" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
         <v>16.8</v>
@@ -5984,10 +6051,10 @@
         <v>10.5</v>
       </c>
       <c r="S31" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="T31" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="U31" t="n">
         <v>24</v>
@@ -6005,19 +6072,19 @@
         <v>4.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6035,13 +6102,13 @@
         <v>9</v>
       </c>
       <c r="AJ31" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK31" t="n">
         <v>6</v>
       </c>
       <c r="AL31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM31" t="n">
         <v>27</v>
@@ -6050,7 +6117,7 @@
         <v>9</v>
       </c>
       <c r="AO31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP31" t="n">
         <v>23</v>
@@ -6077,13 +6144,13 @@
         <v>20</v>
       </c>
       <c r="AX31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY31" t="n">
         <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA31" t="n">
         <v>21</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-15-2014-15</t>
+          <t>2015-04-15</t>
         </is>
       </c>
     </row>
